--- a/results/andar_할인율모니터링_20260910.xlsx
+++ b/results/andar_할인율모니터링_20260910.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H180"/>
+  <dimension ref="A1:H178"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -529,10 +529,14 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>5.0</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -609,7 +613,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>3,555</t>
+          <t>3,557</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -651,7 +655,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>3,555</t>
+          <t>3,557</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -1029,7 +1033,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -1083,27 +1087,27 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=18773&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=5845&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>EPTBG-11</t>
+          <t>EJFMT-01</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>안다르 실버 리유저블백 L</t>
+          <t>릴렉스 에어소프트 요가매트 (8mm)</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>7,500</t>
+          <t>31,000</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>7,500</t>
+          <t>31,000</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1113,39 +1117,39 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>10,082</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>5.0</t>
+          <t>4.8</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=5845&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=18773&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>EJFMT-01</t>
+          <t>EPTBG-11</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>릴렉스 에어소프트 요가매트 (8mm)</t>
+          <t>안다르 실버 리유저블백 L</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>31,000</t>
+          <t>7,500</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>31,000</t>
+          <t>7,500</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1155,12 +1159,12 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>10,080</t>
+          <t>2</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>4.8</t>
+          <t>5.0</t>
         </is>
       </c>
     </row>
@@ -1197,54 +1201,54 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>115</t>
+          <t>116</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>4.7</t>
+          <t>4.8</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=16629&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=13862&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>EPTET-01</t>
+          <t>EOTBG-03</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>언더웨어 파우치</t>
+          <t>데이 앤 트래블 숄더백</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>20,000</t>
+          <t>79,000</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>20,000</t>
+          <t>59,000</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>25%</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>342</t>
+          <t>123</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>4.8</t>
+          <t>4.9</t>
         </is>
       </c>
     </row>
@@ -1281,7 +1285,7 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>8,083</t>
+          <t>8,093</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -1293,42 +1297,42 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=13862&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=16629&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>EOTBG-03</t>
+          <t>EPTET-01</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>데이 앤 트래블 숄더백</t>
+          <t>언더웨어 파우치</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>79,000</t>
+          <t>20,000</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>59,000</t>
+          <t>20,000</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>25%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>123</t>
+          <t>344</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>4.9</t>
+          <t>4.8</t>
         </is>
       </c>
     </row>
@@ -1461,121 +1465,121 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=9620&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=13409&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>EMTBG-12</t>
+          <t>EOTBG-10</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>데일리 쇼퍼백</t>
+          <t>에어플라이 투웨이 프리런 백 3.0</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>65,000</t>
+          <t>35,000</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>49,000</t>
+          <t>32,000</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>25%</t>
+          <t>9%</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>1,407</t>
+          <t>1,138</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>4.8</t>
+          <t>3.0</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=13409&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=15372&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>EOTBG-10</t>
+          <t>EOTBG-16</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>에어플라이 투웨이 프리런 백 3.0</t>
+          <t>폴더블 미니백 2.0</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>35,000</t>
+          <t>39,000</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>32,000</t>
+          <t>29,000</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>9%</t>
+          <t>26%</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>1,138</t>
+          <t>287</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>3.0</t>
+          <t>4.8</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=15372&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=9620&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>EOTBG-16</t>
+          <t>EMTBG-12</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>폴더블 미니백 2.0</t>
+          <t>데일리 쇼퍼백</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>39,000</t>
+          <t>65,000</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>29,000</t>
+          <t>49,000</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>26%</t>
+          <t>25%</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>287</t>
+          <t>1,407</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -1671,37 +1675,37 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=8817&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=17443&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>EMTSC-03</t>
+          <t>EPTSC-04</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>[1&amp;1] 논슬립 서포트 풀 토삭스 (HOLE)</t>
+          <t>[3 SET] 필라테스 삭스</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>21,800</t>
+          <t>41,700</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>17,800</t>
+          <t>30,900</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>18%</t>
+          <t>26%</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>4,820</t>
+          <t>401</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -1718,7 +1722,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>EPTSC-04</t>
+          <t>EPTSC-05</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -1743,7 +1747,7 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>398</t>
+          <t>401</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
@@ -1760,7 +1764,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>EPTSC-05</t>
+          <t>EPTSC-06</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -1785,7 +1789,7 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>398</t>
+          <t>401</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
@@ -1797,121 +1801,121 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=17443&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=15428&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>EPTSC-06</t>
+          <t>EOTBG-20</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>[3 SET] 필라테스 삭스</t>
+          <t>클라우드 스트링 쇼퍼백</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>41,700</t>
+          <t>79,000</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>30,900</t>
+          <t>65,000</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>26%</t>
+          <t>18%</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>398</t>
+          <t>33</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>4.7</t>
+          <t>4.8</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=15428&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=15370&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>EOTBG-20</t>
+          <t>EOTBG-14</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>클라우드 스트링 쇼퍼백</t>
+          <t>폴더블 캐리백 2.0</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>79,000</t>
+          <t>69,000</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>65,000</t>
+          <t>55,000</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>18%</t>
+          <t>20%</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>86</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>4.8</t>
+          <t>4.9</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=15370&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=15143&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>EOTBG-14</t>
+          <t>EOTBG-17</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>폴더블 캐리백 2.0</t>
+          <t>3 in 1 캐리온 더플백</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>69,000</t>
+          <t>109,000</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>55,000</t>
+          <t>85,000</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>20%</t>
+          <t>22%</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>86</t>
+          <t>42</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
@@ -1923,42 +1927,42 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=15143&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=15369&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>EOTBG-17</t>
+          <t>EOTBG-19</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>3 in 1 캐리온 더플백</t>
+          <t>위켄드 호보백</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>109,000</t>
+          <t>79,000</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>85,000</t>
+          <t>59,000</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>22%</t>
+          <t>25%</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>64</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>4.9</t>
+          <t>4.8</t>
         </is>
       </c>
     </row>
@@ -1995,7 +1999,7 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>2,416</t>
+          <t>2,419</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
@@ -2079,7 +2083,7 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>3,201</t>
+          <t>3,202</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
@@ -2121,7 +2125,7 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>3,201</t>
+          <t>3,202</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
@@ -2163,7 +2167,7 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>5,128</t>
+          <t>5,130</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
@@ -2217,84 +2221,84 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=6952&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=15350&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>EJFST-02</t>
+          <t>EOTSC-09</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>릴렉스 요가링</t>
+          <t>[1&amp;1] 컴프레션 러닝 니삭스</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>5,900</t>
+          <t>29,800</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>5,900</t>
+          <t>24,900</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>16%</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>6,585</t>
+          <t>685</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>4.7</t>
+          <t>4.8</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=15350&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=6952&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>EOTSC-09</t>
+          <t>EJFST-02</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>[1&amp;1] 컴프레션 러닝 니삭스</t>
+          <t>릴렉스 요가링</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>29,800</t>
+          <t>5,900</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>24,900</t>
+          <t>5,900</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>16%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>684</t>
+          <t>6,585</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>4.8</t>
+          <t>4.7</t>
         </is>
       </c>
     </row>
@@ -2331,7 +2335,7 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>1,038</t>
+          <t>1,039</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
@@ -2373,7 +2377,7 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>1,038</t>
+          <t>1,039</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
@@ -2427,42 +2431,42 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=8838&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=11456&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>EMTSV-03</t>
+          <t>ENTSC-13</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>[1&amp;1] 서포트 무릎 보호대</t>
+          <t>[1&amp;1] 논슬립 퍼포먼스 삭스</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>27,800</t>
+          <t>23,800</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>22,900</t>
+          <t>17,800</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>18%</t>
+          <t>25%</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>2,009</t>
+          <t>3,022</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>4.5</t>
+          <t>4.7</t>
         </is>
       </c>
     </row>
@@ -2474,7 +2478,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>ENTSC-13</t>
+          <t>ENTSC-14</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -2499,7 +2503,7 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>3,021</t>
+          <t>3,022</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
@@ -2511,42 +2515,42 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=11456&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=8838&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>ENTSC-14</t>
+          <t>EMTSV-03</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>[1&amp;1] 논슬립 퍼포먼스 삭스</t>
+          <t>[1&amp;1] 서포트 무릎 보호대</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>23,800</t>
+          <t>27,800</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>17,800</t>
+          <t>22,900</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>25%</t>
+          <t>18%</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>3,021</t>
+          <t>2,011</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>4.7</t>
+          <t>4.5</t>
         </is>
       </c>
     </row>
@@ -2583,7 +2587,7 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>367</t>
+          <t>369</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
@@ -2667,7 +2671,7 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>10,368</t>
+          <t>10,369</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
@@ -2679,27 +2683,27 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=16844&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=13215&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>EPTET-02</t>
+          <t>EOTCP-01</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>언더웨어 세탁망</t>
+          <t>올라운드 버킷햇</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>9,900</t>
+          <t>69,000</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>9,900</t>
+          <t>69,000</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2709,7 +2713,7 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>293</t>
+          <t>357</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
@@ -2721,27 +2725,27 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=13215&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=16844&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>EOTCP-01</t>
+          <t>EPTET-02</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>올라운드 버킷햇</t>
+          <t>언더웨어 세탁망</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>69,000</t>
+          <t>9,900</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>69,000</t>
+          <t>9,900</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -2751,7 +2755,7 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>357</t>
+          <t>293</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
@@ -2835,7 +2839,7 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>627</t>
+          <t>628</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
@@ -2973,27 +2977,27 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=15408&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=6660&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>EOTSC-14</t>
+          <t>EKPMT-03</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>맨즈 논슬립 풀 토삭스</t>
+          <t>릴렉스 논슬립 요가 타월</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>11,900</t>
+          <t>35,900</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>11,900</t>
+          <t>35,900</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -3003,12 +3007,12 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>104</t>
+          <t>1,559</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>4.6</t>
+          <t>4.8</t>
         </is>
       </c>
     </row>
@@ -3057,27 +3061,27 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=6660&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=15408&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>EKPMT-03</t>
+          <t>EOTSC-14</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>릴렉스 논슬립 요가 타월</t>
+          <t>맨즈 논슬립 풀 토삭스</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>35,900</t>
+          <t>11,900</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>35,900</t>
+          <t>11,900</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -3087,39 +3091,39 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>1,559</t>
+          <t>104</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>4.8</t>
+          <t>4.6</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=11962&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=13854&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>ENTMT-01</t>
+          <t>EOTSC-06</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>레스트 인 마블 요가매트 (4mm)</t>
+          <t>서포트 쿠션 러닝 삭스</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>49,000</t>
+          <t>10,900</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>49,000</t>
+          <t>10,900</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -3129,7 +3133,7 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>269</t>
+          <t>763</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
@@ -3141,27 +3145,27 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=13854&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=11962&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>EOTSC-06</t>
+          <t>ENTMT-01</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>서포트 쿠션 러닝 삭스</t>
+          <t>레스트 인 마블 요가매트 (4mm)</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>10,900</t>
+          <t>49,000</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>10,900</t>
+          <t>49,000</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -3171,7 +3175,7 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>763</t>
+          <t>269</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
@@ -3351,27 +3355,27 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=14085&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=5837&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>EOTSV-04</t>
+          <t>EJFMB-03</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>프리런 라이트 러닝 밴드</t>
+          <t>릴렉스 짐볼 65cm</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>32,000</t>
+          <t>19,000</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>32,000</t>
+          <t>19,000</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -3381,123 +3385,123 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>127</t>
+          <t>2,112</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>4.2</t>
+          <t>4.7</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=10554&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=13604&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>ENTMK-01</t>
+          <t>EOTSV-01</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>UV 프로텍션 맨즈 골프 마스크</t>
+          <t>[1&amp;1] 하이 서포트 무릎 보호대</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>23,000</t>
+          <t>29,800</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>23,000</t>
+          <t>24,900</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>16%</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>1,535</t>
+          <t>706</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>4.8</t>
+          <t>4.7</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=13604&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=14085&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>EOTSV-01</t>
+          <t>EOTSV-04</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>[1&amp;1] 하이 서포트 무릎 보호대</t>
+          <t>프리런 라이트 러닝 밴드</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>29,800</t>
+          <t>32,000</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>24,900</t>
+          <t>32,000</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>16%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>706</t>
+          <t>127</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>4.7</t>
+          <t>4.2</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=5837&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=10554&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>EJFMB-03</t>
+          <t>ENTMK-01</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>릴렉스 짐볼 65cm</t>
+          <t>UV 프로텍션 맨즈 골프 마스크</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>19,000</t>
+          <t>23,000</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>19,000</t>
+          <t>23,000</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -3507,12 +3511,12 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>2,111</t>
+          <t>1,535</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>4.7</t>
+          <t>4.8</t>
         </is>
       </c>
     </row>
@@ -3591,12 +3595,12 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>59</t>
+          <t>60</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>4.9</t>
+          <t>4.8</t>
         </is>
       </c>
     </row>
@@ -3759,7 +3763,7 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>576</t>
+          <t>578</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
@@ -3981,27 +3985,27 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=13859&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=13410&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>ENTSO-12</t>
+          <t>EOTSC-09</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>안다르 제트플라이 (맨즈)</t>
+          <t>컴프레션 러닝 니삭스</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>139,000</t>
+          <t>14,900</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>139,000</t>
+          <t>14,900</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
@@ -4011,39 +4015,39 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>696</t>
+          <t>352</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>4.7</t>
+          <t>4.9</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=13410&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=13859&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>EOTSC-09</t>
+          <t>ENTSO-12</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>컴프레션 러닝 니삭스</t>
+          <t>안다르 제트플라이 (맨즈)</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>14,900</t>
+          <t>139,000</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>14,900</t>
+          <t>139,000</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
@@ -4053,12 +4057,12 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>351</t>
+          <t>696</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>4.9</t>
+          <t>4.7</t>
         </is>
       </c>
     </row>
@@ -4149,27 +4153,27 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=11039&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=15153&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>ENTFB-01</t>
+          <t>EOTSC-13</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>에어쿨링 라인 스크런치</t>
+          <t>테이핑 테크 러닝 삭스</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>8,900</t>
+          <t>13,900</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>8,900</t>
+          <t>13,900</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
@@ -4179,7 +4183,7 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>770</t>
+          <t>275</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
@@ -4191,27 +4195,27 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=16032&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=6661&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>EOTCP-05</t>
+          <t>EKPMB-01</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>히트 런 이어플랩 캡</t>
+          <t>릴렉스 웨이트볼 0.5kg</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>55,000</t>
+          <t>6,900</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>55,000</t>
+          <t>6,900</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
@@ -4221,39 +4225,39 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>92</t>
+          <t>694</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>4.8</t>
+          <t>4.7</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=15153&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=6664&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>EOTSC-13</t>
+          <t>EKPRB-04</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>테이핑 테크 러닝 삭스</t>
+          <t>릴렉스 3레벨 스트레칭 롱밴드</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>13,900</t>
+          <t>34,900</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>13,900</t>
+          <t>34,900</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
@@ -4263,39 +4267,39 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>274</t>
+          <t>469</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>4.8</t>
+          <t>4.7</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=6664&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=11039&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>EKPRB-04</t>
+          <t>ENTFB-01</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>릴렉스 3레벨 스트레칭 롱밴드</t>
+          <t>에어쿨링 라인 스크런치</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>34,900</t>
+          <t>8,900</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>34,900</t>
+          <t>8,900</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
@@ -4305,39 +4309,39 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>469</t>
+          <t>770</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>4.7</t>
+          <t>4.8</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=6661&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=16032&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>EKPMB-01</t>
+          <t>EOTCP-05</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>릴렉스 웨이트볼 0.5kg</t>
+          <t>히트 런 이어플랩 캡</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>6,900</t>
+          <t>55,000</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>6,900</t>
+          <t>55,000</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
@@ -4347,39 +4351,39 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>693</t>
+          <t>92</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>4.7</t>
+          <t>4.8</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=16660&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=13407&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>EOTET-03</t>
+          <t>EOTSV-03</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>맨즈 라이트 러닝 베스트</t>
+          <t>서포트 허리 보호대</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>79,000</t>
+          <t>34,000</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>79,000</t>
+          <t>34,000</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
@@ -4389,39 +4393,39 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>183</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>4.6</t>
+          <t>4.7</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=13408&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=16660&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>EOTSC-01</t>
+          <t>EOTET-03</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>프레시 필드 니삭스</t>
+          <t>맨즈 라이트 러닝 베스트</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>14,900</t>
+          <t>79,000</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>14,900</t>
+          <t>79,000</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
@@ -4431,39 +4435,39 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>299</t>
+          <t>12</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>4.8</t>
+          <t>4.6</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=13407&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=16847&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>EOTSV-03</t>
+          <t>EPTSC-02</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>서포트 허리 보호대</t>
+          <t>하이 쿠션 테이핑 러닝 삭스</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>34,000</t>
+          <t>12,900</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>34,000</t>
+          <t>12,900</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
@@ -4473,7 +4477,7 @@
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>183</t>
+          <t>94</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
@@ -4485,27 +4489,27 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=16847&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=13408&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>EPTSC-02</t>
+          <t>EOTSC-01</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>하이 쿠션 테이핑 러닝 삭스</t>
+          <t>프레시 필드 니삭스</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>12,900</t>
+          <t>14,900</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>12,900</t>
+          <t>14,900</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
@@ -4515,54 +4519,54 @@
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>94</t>
+          <t>299</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>4.7</t>
+          <t>4.8</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=10953&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=6662&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>ENTSC-07</t>
+          <t>EKPMB-02</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>[3 SET] 에어컴피 크루 삭스</t>
+          <t>릴렉스 미니 짐볼</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>51,000</t>
+          <t>13,000</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>29,000</t>
+          <t>13,000</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>43%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>561</t>
+          <t>1,224</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>4.9</t>
+          <t>4.6</t>
         </is>
       </c>
     </row>
@@ -4599,7 +4603,7 @@
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>1,090</t>
+          <t>1,091</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
@@ -4653,69 +4657,69 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=13404&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=10953&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>EOTGL-01</t>
+          <t>ENTSC-07</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>짐 글러브 2.0</t>
+          <t>[3 SET] 에어컴피 크루 삭스</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>25,000</t>
+          <t>51,000</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>25,000</t>
+          <t>29,000</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>43%</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>287</t>
+          <t>561</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>4.8</t>
+          <t>4.9</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=14562&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=13404&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>EOTBG-11</t>
+          <t>EOTGL-01</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>메쉬 파우치</t>
+          <t>짐 글러브 2.0</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>29,000</t>
+          <t>25,000</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>29,000</t>
+          <t>25,000</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
@@ -4725,12 +4729,12 @@
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>192</t>
+          <t>287</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>4.7</t>
+          <t>4.8</t>
         </is>
       </c>
     </row>
@@ -4779,27 +4783,27 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=13851&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=14562&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>EOTCP-03</t>
+          <t>EOTBG-11</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>쿨 라운드 볼캡</t>
+          <t>메쉬 파우치</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>45,000</t>
+          <t>29,000</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>45,000</t>
+          <t>29,000</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
@@ -4809,39 +4813,39 @@
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>102</t>
+          <t>192</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>4.8</t>
+          <t>4.7</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=17424&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=13851&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>EPTSC-05</t>
+          <t>EOTCP-03</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>필라테스 앵클 삭스</t>
+          <t>쿨 라운드 볼캡</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>13,900</t>
+          <t>45,000</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>13,900</t>
+          <t>45,000</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
@@ -4851,39 +4855,39 @@
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>102</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>4.9</t>
+          <t>4.8</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=11457&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=17424&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>ENTSC-12</t>
+          <t>EPTSC-05</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>논슬립 퍼포먼스 토삭스</t>
+          <t>필라테스 앵클 삭스</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>12,900</t>
+          <t>13,900</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>12,900</t>
+          <t>13,900</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
@@ -4893,39 +4897,39 @@
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>4,135</t>
+          <t>41</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>4.7</t>
+          <t>4.9</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=14084&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=11457&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>EOTET-01</t>
+          <t>ENTSC-12</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>소프트 뱀부 롱 타월</t>
+          <t>논슬립 퍼포먼스 토삭스</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>19,900</t>
+          <t>12,900</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>19,900</t>
+          <t>12,900</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
@@ -4935,12 +4939,12 @@
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>238</t>
+          <t>4,135</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>4.8</t>
+          <t>4.7</t>
         </is>
       </c>
     </row>
@@ -4989,27 +4993,27 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=16637&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=14084&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>EPTFB-02</t>
+          <t>EOTET-01</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>퍼포먼스 심리스 손목밴드</t>
+          <t>소프트 뱀부 롱 타월</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>6,900</t>
+          <t>19,900</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>6,900</t>
+          <t>19,900</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
@@ -5019,7 +5023,7 @@
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>272</t>
+          <t>238</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
@@ -5031,37 +5035,37 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=10657&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=16637&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>EMTSC-17</t>
+          <t>EPTFB-02</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>[3 SET] 맨즈 클래식 삭스</t>
+          <t>퍼포먼스 심리스 손목밴드</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>20,700</t>
+          <t>6,900</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>17,900</t>
+          <t>6,900</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>14%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>223</t>
+          <t>273</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
@@ -5073,121 +5077,121 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=12778&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=8837&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>ENTBG-14</t>
+          <t>EMTSV-02</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>웨이브 패딩 파우치</t>
+          <t>[1&amp;1] 서포트 발목 보호대</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>32,000</t>
+          <t>27,800</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>32,000</t>
+          <t>22,900</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>18%</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>192</t>
+          <t>717</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>4.8</t>
+          <t>4.7</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=15369&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=8836&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>EOTBG-19</t>
+          <t>EMTSV-01</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>위켄드 호보백</t>
+          <t>[1&amp;1] 서포트 팔꿈치 보호대</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>79,000</t>
+          <t>27,800</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>59,000</t>
+          <t>22,900</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>25%</t>
+          <t>18%</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>64</t>
+          <t>591</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>4.8</t>
+          <t>4.7</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=8837&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=12096&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>EMTSV-02</t>
+          <t>ENTET-02</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>[1&amp;1] 서포트 발목 보호대</t>
+          <t>릴렉스 소프트 웨이트바 2kg</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>27,800</t>
+          <t>39,000</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>22,900</t>
+          <t>39,000</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>18%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>717</t>
+          <t>76</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
@@ -5199,59 +5203,59 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=8836&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=10657&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>EMTSV-01</t>
+          <t>EMTSC-17</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>[1&amp;1] 서포트 팔꿈치 보호대</t>
+          <t>[3 SET] 맨즈 클래식 삭스</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>27,800</t>
+          <t>20,700</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>22,900</t>
+          <t>17,900</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>18%</t>
+          <t>14%</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>591</t>
+          <t>223</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>4.7</t>
+          <t>4.8</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=12096&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=5145&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>ENTET-02</t>
+          <t>EJPFR-04</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>릴렉스 소프트 웨이트바 2kg</t>
+          <t>릴렉스 폼롤러 Ⅱ</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
@@ -5271,39 +5275,39 @@
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>76</t>
+          <t>6,363</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>4.7</t>
+          <t>4.8</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=5145&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=16031&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>EJPFR-04</t>
+          <t>EOTGL-02</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>릴렉스 폼롤러 Ⅱ</t>
+          <t>히트 런 글러브</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>39,000</t>
+          <t>29,000</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>39,000</t>
+          <t>29,000</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
@@ -5313,12 +5317,12 @@
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>6,363</t>
+          <t>212</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>4.8</t>
+          <t>4.7</t>
         </is>
       </c>
     </row>
@@ -5367,27 +5371,27 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=16031&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=8578&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>EOTGL-02</t>
+          <t>EMTSC-01</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>히트 런 글러브</t>
+          <t>링글 크루 삭스</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>29,000</t>
+          <t>7,900</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>29,000</t>
+          <t>7,900</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
@@ -5397,39 +5401,39 @@
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>212</t>
+          <t>1,328</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>4.7</t>
+          <t>4.8</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=8578&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=17440&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>EMTSC-01</t>
+          <t>EPTET-03</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>링글 크루 삭스</t>
+          <t>안다르 3단 양우산</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>7,900</t>
+          <t>29,000</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>7,900</t>
+          <t>29,000</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
@@ -5439,39 +5443,39 @@
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>1,328</t>
+          <t>36</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>4.8</t>
+          <t>4.4</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=17440&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=13805&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>EPTET-03</t>
+          <t>EOTSC-04</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>안다르 3단 양우산</t>
+          <t>올데이 수피마 스니커즈 삭스</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>29,000</t>
+          <t>5,900</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>29,000</t>
+          <t>5,900</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
@@ -5481,39 +5485,39 @@
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>429</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>4.4</t>
+          <t>4.8</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=13805&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=15732&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>EOTSC-04</t>
+          <t>EOTSC-11</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>올데이 수피마 스니커즈 삭스</t>
+          <t>웜 레그 롱 워머</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>5,900</t>
+          <t>25,000</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>5,900</t>
+          <t>25,000</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
@@ -5523,7 +5527,7 @@
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>429</t>
+          <t>113</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
@@ -5535,42 +5539,42 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=6662&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=17522&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>EKPMB-02</t>
+          <t>EPTSC-07</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>릴렉스 미니 짐볼</t>
+          <t>[1&amp;1] 맨즈 필라테스 삭스</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>13,000</t>
+          <t>27,800</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>13,000</t>
+          <t>20,900</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>25%</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>1,224</t>
+          <t>29</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>4.6</t>
+          <t>4.9</t>
         </is>
       </c>
     </row>
@@ -5582,7 +5586,7 @@
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>EPTSC-07</t>
+          <t>EPTSC-08</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
@@ -5619,79 +5623,79 @@
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=17522&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=13605&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>EPTSC-08</t>
+          <t>EOTSV-02</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>[1&amp;1] 맨즈 필라테스 삭스</t>
+          <t>[1&amp;1] 하이 서포트 팔꿈치 보호대</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>27,800</t>
+          <t>29,800</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>20,900</t>
+          <t>24,900</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>25%</t>
+          <t>16%</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>154</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>4.9</t>
+          <t>4.8</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=13605&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=12778&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>EOTSV-02</t>
+          <t>ENTBG-14</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>[1&amp;1] 하이 서포트 팔꿈치 보호대</t>
+          <t>웨이브 패딩 파우치</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>29,800</t>
+          <t>32,000</t>
         </is>
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>24,900</t>
+          <t>32,000</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>16%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>154</t>
+          <t>194</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
@@ -5703,27 +5707,27 @@
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=15732&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=12793&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>EOTSC-11</t>
+          <t>ENTMU-01</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>웜 레그 롱 워머</t>
+          <t>소프트 니트 머플러</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>25,000</t>
+          <t>19,900</t>
         </is>
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>25,000</t>
+          <t>19,900</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
@@ -5733,7 +5737,7 @@
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>113</t>
+          <t>472</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
@@ -5745,27 +5749,27 @@
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=13566&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=9996&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>EOTSC-10</t>
+          <t>EMTSC-27</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>시그니처 로고 맨즈 크루 삭스</t>
+          <t>올라운드 오버 니삭스</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>7,900</t>
+          <t>13,900</t>
         </is>
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>7,900</t>
+          <t>13,900</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
@@ -5775,49 +5779,49 @@
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>214</t>
+          <t>296</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>4.8</t>
+          <t>4.7</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=9996&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=11130&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>EMTSC-27</t>
+          <t>ENTSV-01</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>올라운드 오버 니삭스</t>
+          <t>[1&amp;1] 3D 쿨링 팔토시</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>13,900</t>
+          <t>29,800</t>
         </is>
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>13,900</t>
+          <t>25,900</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>13%</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>296</t>
+          <t>552</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
@@ -5829,121 +5833,121 @@
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=9612&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=17386&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>EMTSC-28</t>
+          <t>EPTSC-07</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>[1&amp;1] 리브드 셔링 루즈 삭스</t>
+          <t>맨즈 필라테스 앵클 삭스</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>21,800</t>
+          <t>13,900</t>
         </is>
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>17,900</t>
+          <t>13,900</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>18%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>395</t>
+          <t>7</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>4.7</t>
+          <t>5.0</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=11130&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=10191&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>ENTSV-01</t>
+          <t>EMTSC-26</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>[1&amp;1] 3D 쿨링 팔토시</t>
+          <t>[1&amp;1] 램스울 크루 삭스</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>29,800</t>
+          <t>19,800</t>
         </is>
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>25,900</t>
+          <t>17,900</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>13%</t>
+          <t>10%</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>552</t>
+          <t>840</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>4.7</t>
+          <t>4.8</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=17857&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=16036&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>EPTSC-03</t>
+          <t>EOTCP-06</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>[1&amp;1] 데일리 루즈 삭스</t>
+          <t>소프트 니트 버킷햇</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>23,800</t>
+          <t>45,000</t>
         </is>
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>18,900</t>
+          <t>45,000</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>21%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>52</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
@@ -5955,27 +5959,27 @@
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=12793&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=13566&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>ENTMU-01</t>
+          <t>EOTSC-10</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>소프트 니트 머플러</t>
+          <t>시그니처 로고 맨즈 크루 삭스</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>19,900</t>
+          <t>7,900</t>
         </is>
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>19,900</t>
+          <t>7,900</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
@@ -5985,7 +5989,7 @@
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>472</t>
+          <t>214</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
@@ -5997,111 +6001,111 @@
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=17386&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=9612&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>EPTSC-07</t>
+          <t>EMTSC-28</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>맨즈 필라테스 앵클 삭스</t>
+          <t>[1&amp;1] 리브드 셔링 루즈 삭스</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>13,900</t>
+          <t>21,800</t>
         </is>
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>13,900</t>
+          <t>17,900</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>18%</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>395</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>5.0</t>
+          <t>4.7</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=10191&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=8769&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>EMTSC-26</t>
+          <t>EMTSV-02</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>[1&amp;1] 램스울 크루 삭스</t>
+          <t>서포트 발목 보호대</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>19,800</t>
+          <t>13,900</t>
         </is>
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>17,900</t>
+          <t>13,900</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>10%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>840</t>
+          <t>717</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>4.8</t>
+          <t>4.7</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=16036&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=11061&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>EOTCP-06</t>
+          <t>ENTSV-01</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>소프트 니트 버킷햇</t>
+          <t>3D 쿨링 팔토시</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>45,000</t>
+          <t>14,900</t>
         </is>
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>45,000</t>
+          <t>14,900</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
@@ -6111,81 +6115,81 @@
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>52</t>
+          <t>552</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>4.8</t>
+          <t>4.7</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=8769&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=17857&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>EMTSV-02</t>
+          <t>EPTSC-03</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>서포트 발목 보호대</t>
+          <t>[1&amp;1] 데일리 루즈 삭스</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>13,900</t>
+          <t>23,800</t>
         </is>
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>13,900</t>
+          <t>18,900</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>21%</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>717</t>
+          <t>28</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>4.7</t>
+          <t>4.8</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=11061&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=8728&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>ENTSV-01</t>
+          <t>EMTSC-05</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>3D 쿨링 팔토시</t>
+          <t>논슬립 서포트 하프 토삭스 (SOLID)</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>14,900</t>
+          <t>9,900</t>
         </is>
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>14,900</t>
+          <t>9,900</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
@@ -6195,39 +6199,39 @@
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>552</t>
+          <t>565</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>4.7</t>
+          <t>4.8</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=8728&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=13806&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>EMTSC-05</t>
+          <t>EOTSC-05</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>논슬립 서포트 하프 토삭스 (SOLID)</t>
+          <t>올데이 수피마 앵클 삭스</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>9,900</t>
+          <t>6,900</t>
         </is>
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>9,900</t>
+          <t>6,900</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
@@ -6237,39 +6241,39 @@
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>565</t>
+          <t>476</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>4.8</t>
+          <t>4.7</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=13806&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=6665&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>EOTSC-05</t>
+          <t>EKPRB-05</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>올데이 수피마 앵클 삭스</t>
+          <t>릴렉스 4레벨 힙 밴드</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>6,900</t>
+          <t>21,900</t>
         </is>
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>6,900</t>
+          <t>21,900</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
@@ -6279,49 +6283,49 @@
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>476</t>
+          <t>527</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>4.7</t>
+          <t>4.8</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=6665&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=15867&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>EKPRB-05</t>
+          <t>EOTSC-18</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>릴렉스 4레벨 힙 밴드</t>
+          <t>[1&amp;1] 올데이 기모 삭스</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>21,900</t>
+          <t>21,800</t>
         </is>
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>21,900</t>
+          <t>15,900</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>27%</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>527</t>
+          <t>225</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
@@ -6333,69 +6337,69 @@
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=15867&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=13405&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>EOTSC-18</t>
+          <t>EOTSV-01</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>[1&amp;1] 올데이 기모 삭스</t>
+          <t>하이 서포트 무릎 보호대</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>21,800</t>
+          <t>14,900</t>
         </is>
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>15,900</t>
+          <t>14,900</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>27%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>225</t>
+          <t>706</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>4.8</t>
+          <t>4.7</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=13405&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=15376&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>EOTSV-01</t>
+          <t>EOTSC-17</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>하이 서포트 무릎 보호대</t>
+          <t>논슬립 스킨 토삭스</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>14,900</t>
+          <t>12,900</t>
         </is>
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>14,900</t>
+          <t>12,900</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
@@ -6405,7 +6409,7 @@
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>706</t>
+          <t>88</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
@@ -6417,27 +6421,27 @@
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=15376&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=14561&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>EOTSC-17</t>
+          <t>EOTBG-05</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>논슬립 스킨 토삭스</t>
+          <t>메쉬 포켓 비치백</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>12,900</t>
+          <t>49,000</t>
         </is>
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>12,900</t>
+          <t>49,000</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
@@ -6447,39 +6451,39 @@
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>88</t>
+          <t>60</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>4.7</t>
+          <t>4.8</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=14561&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=12488&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>EOTBG-05</t>
+          <t>ENTBG-10</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>메쉬 포켓 비치백</t>
+          <t>스퀘어 크로스백</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>49,000</t>
+          <t>79,000</t>
         </is>
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>49,000</t>
+          <t>79,000</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
@@ -6489,7 +6493,7 @@
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>59</t>
+          <t>632</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
@@ -6501,27 +6505,27 @@
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=12488&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=12783&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>ENTBG-10</t>
+          <t>ENTSC-26</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>스퀘어 크로스백</t>
+          <t>니트 기모 오버 니삭스</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>79,000</t>
+          <t>17,900</t>
         </is>
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>79,000</t>
+          <t>17,900</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
@@ -6531,7 +6535,7 @@
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>632</t>
+          <t>354</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
@@ -6543,27 +6547,27 @@
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=12783&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=8768&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>ENTSC-26</t>
+          <t>EMTSV-01</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>니트 기모 오버 니삭스</t>
+          <t>서포트 팔꿈치 보호대</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>17,900</t>
+          <t>13,900</t>
         </is>
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>17,900</t>
+          <t>13,900</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
@@ -6573,39 +6577,39 @@
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>354</t>
+          <t>591</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>4.8</t>
+          <t>4.7</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=8768&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=8727&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>EMTSV-01</t>
+          <t>EMTSC-04</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>서포트 팔꿈치 보호대</t>
+          <t>논슬립 서포트 하프 토삭스 (HOLE)</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>13,900</t>
+          <t>10,900</t>
         </is>
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>13,900</t>
+          <t>10,900</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
@@ -6615,39 +6619,39 @@
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>591</t>
+          <t>645</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>4.7</t>
+          <t>4.8</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=8727&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=12794&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>EMTSC-04</t>
+          <t>ENTFB-05</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>논슬립 서포트 하프 토삭스 (HOLE)</t>
+          <t>소프트 니트 헤드밴드</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>10,900</t>
+          <t>15,900</t>
         </is>
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>10,900</t>
+          <t>15,900</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
@@ -6657,7 +6661,7 @@
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>645</t>
+          <t>913</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
@@ -6669,27 +6673,27 @@
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=12794&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=12480&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>ENTFB-05</t>
+          <t>ENTSC-24</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>소프트 니트 헤드밴드</t>
+          <t>웜 슬릿 레그 워머</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>15,900</t>
+          <t>29,000</t>
         </is>
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>15,900</t>
+          <t>29,000</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
@@ -6699,12 +6703,12 @@
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>913</t>
+          <t>297</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>4.8</t>
+          <t>4.6</t>
         </is>
       </c>
     </row>
@@ -6825,7 +6829,7 @@
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>260</t>
+          <t>264</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
@@ -6879,37 +6883,37 @@
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=6666&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=15719&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>EKPET-01</t>
+          <t>EOTSC-19</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>릴렉스 소프트 웨이트바 1kg</t>
+          <t>[1&amp;1] 레그 워머</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>20,900</t>
+          <t>21,800</t>
         </is>
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>20,900</t>
+          <t>15,900</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>27%</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>595</t>
+          <t>230</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
@@ -6921,69 +6925,69 @@
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=8770&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=15719&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>EMTSV-03</t>
+          <t>EOTSC-20</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>서포트 무릎 보호대</t>
+          <t>[1&amp;1] 레그 워머</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>13,900</t>
+          <t>21,800</t>
         </is>
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>13,900</t>
+          <t>15,900</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>27%</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>2,009</t>
+          <t>230</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t>4.5</t>
+          <t>4.8</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=12795&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=6666&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>ENTCP-05</t>
+          <t>EKPET-01</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>소프트 니트 비니</t>
+          <t>릴렉스 소프트 웨이트바 1kg</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>19,900</t>
+          <t>20,900</t>
         </is>
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>19,900</t>
+          <t>20,900</t>
         </is>
       </c>
       <c r="F157" t="inlineStr">
@@ -6993,39 +6997,39 @@
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>362</t>
+          <t>595</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>4.7</t>
+          <t>4.8</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=11963&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=8770&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>ENTSC-19</t>
+          <t>EMTSV-03</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>맨즈 논슬립 하프 토삭스</t>
+          <t>서포트 무릎 보호대</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>11,900</t>
+          <t>13,900</t>
         </is>
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>11,900</t>
+          <t>13,900</t>
         </is>
       </c>
       <c r="F158" t="inlineStr">
@@ -7035,39 +7039,39 @@
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>93</t>
+          <t>2,011</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t>4.7</t>
+          <t>4.5</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=11092&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=12795&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>ENTSC-05</t>
+          <t>ENTCP-05</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>에어프레시 크루 삭스</t>
+          <t>소프트 니트 비니</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>17,000</t>
+          <t>19,900</t>
         </is>
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>17,000</t>
+          <t>19,900</t>
         </is>
       </c>
       <c r="F159" t="inlineStr">
@@ -7077,49 +7081,49 @@
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>575</t>
+          <t>362</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t>4.8</t>
+          <t>4.7</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=16632&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=11963&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>EPTSV-02</t>
+          <t>ENTSC-19</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>[1&amp;1] 하이 서포트 발목 보호대</t>
+          <t>맨즈 논슬립 하프 토삭스</t>
         </is>
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>29,800</t>
+          <t>11,900</t>
         </is>
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>24,900</t>
+          <t>11,900</t>
         </is>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>16%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>110</t>
+          <t>93</t>
         </is>
       </c>
       <c r="H160" t="inlineStr">
@@ -7131,27 +7135,27 @@
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=8579&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=11092&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>EMTSC-02</t>
+          <t>ENTSC-05</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>링글 니삭스</t>
+          <t>에어프레시 크루 삭스</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>9,900</t>
+          <t>17,000</t>
         </is>
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>9,900</t>
+          <t>17,000</t>
         </is>
       </c>
       <c r="F161" t="inlineStr">
@@ -7161,7 +7165,7 @@
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>1,700</t>
+          <t>575</t>
         </is>
       </c>
       <c r="H161" t="inlineStr">
@@ -7173,42 +7177,42 @@
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=12480&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=16632&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>ENTSC-24</t>
+          <t>EPTSV-02</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>웜 슬릿 레그 워머</t>
+          <t>[1&amp;1] 하이 서포트 발목 보호대</t>
         </is>
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>29,000</t>
+          <t>29,800</t>
         </is>
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>29,000</t>
+          <t>24,900</t>
         </is>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>16%</t>
         </is>
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>297</t>
+          <t>110</t>
         </is>
       </c>
       <c r="H162" t="inlineStr">
         <is>
-          <t>4.6</t>
+          <t>4.7</t>
         </is>
       </c>
     </row>
@@ -7341,37 +7345,37 @@
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=15719&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=9988&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>EOTSC-19</t>
+          <t>EMTSC-26</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>[1&amp;1] 레그 워머</t>
+          <t>램스울 크루 삭스</t>
         </is>
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>21,800</t>
+          <t>9,900</t>
         </is>
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>15,900</t>
+          <t>9,900</t>
         </is>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>27%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>230</t>
+          <t>332</t>
         </is>
       </c>
       <c r="H166" t="inlineStr">
@@ -7383,22 +7387,22 @@
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=15719&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=16035&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>EOTSC-20</t>
+          <t>EOTSC-12</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>[1&amp;1] 레그 워머</t>
+          <t>소프트 니트 기모 니삭스</t>
         </is>
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>21,800</t>
+          <t>15,900</t>
         </is>
       </c>
       <c r="E167" t="inlineStr">
@@ -7408,44 +7412,44 @@
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>27%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>230</t>
+          <t>102</t>
         </is>
       </c>
       <c r="H167" t="inlineStr">
         <is>
-          <t>4.8</t>
+          <t>5.0</t>
         </is>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=9988&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=13406&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>EMTSC-26</t>
+          <t>EOTSV-02</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>램스울 크루 삭스</t>
+          <t>하이 서포트 팔꿈치 보호대</t>
         </is>
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>9,900</t>
+          <t>14,900</t>
         </is>
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t>9,900</t>
+          <t>14,900</t>
         </is>
       </c>
       <c r="F168" t="inlineStr">
@@ -7455,7 +7459,7 @@
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>332</t>
+          <t>154</t>
         </is>
       </c>
       <c r="H168" t="inlineStr">
@@ -7467,69 +7471,69 @@
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=16035&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=10939&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>EOTSC-12</t>
+          <t>ENTSC-07</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>소프트 니트 기모 니삭스</t>
+          <t>에어컴피 크루 삭스</t>
         </is>
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>15,900</t>
+          <t>17,000</t>
         </is>
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>15,900</t>
+          <t>12,000</t>
         </is>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>29%</t>
         </is>
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>102</t>
+          <t>562</t>
         </is>
       </c>
       <c r="H169" t="inlineStr">
         <is>
-          <t>5.0</t>
+          <t>4.9</t>
         </is>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=13406&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=17842&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>EOTSV-02</t>
+          <t>EPTSC-03</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>하이 서포트 팔꿈치 보호대</t>
+          <t>데일리 루즈 삭스</t>
         </is>
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>14,900</t>
+          <t>11,900</t>
         </is>
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>14,900</t>
+          <t>11,900</t>
         </is>
       </c>
       <c r="F170" t="inlineStr">
@@ -7539,7 +7543,7 @@
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>154</t>
+          <t>28</t>
         </is>
       </c>
       <c r="H170" t="inlineStr">
@@ -7551,69 +7555,69 @@
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=10939&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=9599&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>ENTSC-07</t>
+          <t>EMTSC-28</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>에어컴피 크루 삭스</t>
+          <t>리브드 셔링 루즈 삭스</t>
         </is>
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>17,000</t>
+          <t>10,900</t>
         </is>
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>12,000</t>
+          <t>10,900</t>
         </is>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>29%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>561</t>
+          <t>395</t>
         </is>
       </c>
       <c r="H171" t="inlineStr">
         <is>
-          <t>4.9</t>
+          <t>4.7</t>
         </is>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=17842&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=9993&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>EPTSC-03</t>
+          <t>EMTSC-29</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>데일리 루즈 삭스</t>
+          <t>니트 루즈 삭스</t>
         </is>
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>11,900</t>
+          <t>9,900</t>
         </is>
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>11,900</t>
+          <t>9,900</t>
         </is>
       </c>
       <c r="F172" t="inlineStr">
@@ -7623,7 +7627,7 @@
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>513</t>
         </is>
       </c>
       <c r="H172" t="inlineStr">
@@ -7635,27 +7639,27 @@
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=9599&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=16640&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>EMTSC-28</t>
+          <t>EPTBG-05</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>리브드 셔링 루즈 삭스</t>
+          <t>안다르 시그니처 로고 에코백</t>
         </is>
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>10,900</t>
+          <t>39,000</t>
         </is>
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>10,900</t>
+          <t>39,000</t>
         </is>
       </c>
       <c r="F173" t="inlineStr">
@@ -7665,39 +7669,39 @@
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>395</t>
+          <t>11</t>
         </is>
       </c>
       <c r="H173" t="inlineStr">
         <is>
-          <t>4.7</t>
+          <t>4.3</t>
         </is>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=9993&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=16045&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>EMTSC-29</t>
+          <t>EOTMU-01</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>니트 루즈 삭스</t>
+          <t>스트링 패딩 넥워머</t>
         </is>
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>9,900</t>
+          <t>49,000</t>
         </is>
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>9,900</t>
+          <t>49,000</t>
         </is>
       </c>
       <c r="F174" t="inlineStr">
@@ -7707,39 +7711,39 @@
       </c>
       <c r="G174" t="inlineStr">
         <is>
-          <t>513</t>
+          <t>46</t>
         </is>
       </c>
       <c r="H174" t="inlineStr">
         <is>
-          <t>4.8</t>
+          <t>4.7</t>
         </is>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=16640&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=15733&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>EPTBG-05</t>
+          <t>EOTSC-19</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>안다르 시그니처 로고 에코백</t>
+          <t>레그 숏 워머</t>
         </is>
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t>39,000</t>
+          <t>10,900</t>
         </is>
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>39,000</t>
+          <t>10,900</t>
         </is>
       </c>
       <c r="F175" t="inlineStr">
@@ -7749,39 +7753,39 @@
       </c>
       <c r="G175" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>13</t>
         </is>
       </c>
       <c r="H175" t="inlineStr">
         <is>
-          <t>4.3</t>
+          <t>4.8</t>
         </is>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=16045&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=15734&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>EOTMU-01</t>
+          <t>EOTSC-20</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>스트링 패딩 넥워머</t>
+          <t>레그 미들 워머</t>
         </is>
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>49,000</t>
+          <t>12,900</t>
         </is>
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>49,000</t>
+          <t>12,900</t>
         </is>
       </c>
       <c r="F176" t="inlineStr">
@@ -7791,39 +7795,39 @@
       </c>
       <c r="G176" t="inlineStr">
         <is>
-          <t>46</t>
+          <t>36</t>
         </is>
       </c>
       <c r="H176" t="inlineStr">
         <is>
-          <t>4.7</t>
+          <t>4.9</t>
         </is>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=15734&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=13831&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>EOTSC-20</t>
+          <t>EOTCP-02</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>레그 미들 워머</t>
+          <t>데님 로고 볼캡</t>
         </is>
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t>12,900</t>
+          <t>39,000</t>
         </is>
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t>12,900</t>
+          <t>39,000</t>
         </is>
       </c>
       <c r="F177" t="inlineStr">
@@ -7833,39 +7837,39 @@
       </c>
       <c r="G177" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>26</t>
         </is>
       </c>
       <c r="H177" t="inlineStr">
         <is>
-          <t>4.9</t>
+          <t>4.8</t>
         </is>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=15733&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=11110&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>EOTSC-19</t>
+          <t>ENTCP-01</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>레그 숏 워머</t>
+          <t>와이드 셰이드 버킷햇</t>
         </is>
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t>10,900</t>
+          <t>59,000</t>
         </is>
       </c>
       <c r="E178" t="inlineStr">
         <is>
-          <t>10,900</t>
+          <t>59,000</t>
         </is>
       </c>
       <c r="F178" t="inlineStr">
@@ -7875,94 +7879,10 @@
       </c>
       <c r="G178" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>685</t>
         </is>
       </c>
       <c r="H178" t="inlineStr">
-        <is>
-          <t>4.8</t>
-        </is>
-      </c>
-    </row>
-    <row r="179">
-      <c r="A179" t="inlineStr">
-        <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=13831&amp;cate_no=2100&amp;display_group=1</t>
-        </is>
-      </c>
-      <c r="B179" t="inlineStr">
-        <is>
-          <t>EOTCP-02</t>
-        </is>
-      </c>
-      <c r="C179" t="inlineStr">
-        <is>
-          <t>데님 로고 볼캡</t>
-        </is>
-      </c>
-      <c r="D179" t="inlineStr">
-        <is>
-          <t>39,000</t>
-        </is>
-      </c>
-      <c r="E179" t="inlineStr">
-        <is>
-          <t>39,000</t>
-        </is>
-      </c>
-      <c r="F179" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="G179" t="inlineStr">
-        <is>
-          <t>26</t>
-        </is>
-      </c>
-      <c r="H179" t="inlineStr">
-        <is>
-          <t>4.8</t>
-        </is>
-      </c>
-    </row>
-    <row r="180">
-      <c r="A180" t="inlineStr">
-        <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=11110&amp;cate_no=2100&amp;display_group=1</t>
-        </is>
-      </c>
-      <c r="B180" t="inlineStr">
-        <is>
-          <t>ENTCP-01</t>
-        </is>
-      </c>
-      <c r="C180" t="inlineStr">
-        <is>
-          <t>와이드 셰이드 버킷햇</t>
-        </is>
-      </c>
-      <c r="D180" t="inlineStr">
-        <is>
-          <t>59,000</t>
-        </is>
-      </c>
-      <c r="E180" t="inlineStr">
-        <is>
-          <t>59,000</t>
-        </is>
-      </c>
-      <c r="F180" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="G180" t="inlineStr">
-        <is>
-          <t>685</t>
-        </is>
-      </c>
-      <c r="H180" t="inlineStr">
         <is>
           <t>4.7</t>
         </is>
